--- a/data/descargas/corte_caja_2026-02.xlsx
+++ b/data/descargas/corte_caja_2026-02.xlsx
@@ -573,7 +573,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reporte generado: 01-03-2026 07:20 a. m. </t>
+          <t xml:space="preserve">Reporte generado: 01-03-2026 07:47 a. m. </t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
